--- a/artfynd/A 37165-2026 artfynd.xlsx
+++ b/artfynd/A 37165-2026 artfynd.xlsx
@@ -2316,7 +2316,7 @@
         <v>81135642</v>
       </c>
       <c r="B18" t="n">
-        <v>58057</v>
+        <v>58110</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 37165-2026 artfynd.xlsx
+++ b/artfynd/A 37165-2026 artfynd.xlsx
@@ -2316,7 +2316,7 @@
         <v>81135642</v>
       </c>
       <c r="B18" t="n">
-        <v>58110</v>
+        <v>58112</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 37165-2026 artfynd.xlsx
+++ b/artfynd/A 37165-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068262</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92068</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137068264</v>
       </c>
       <c r="B3" t="n">
-        <v>92067</v>
+        <v>92068</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137068052</v>
       </c>
       <c r="B4" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137068074</v>
       </c>
       <c r="B5" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137068079</v>
       </c>
       <c r="B6" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137068089</v>
       </c>
       <c r="B7" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137068266</v>
       </c>
       <c r="B8" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137068268</v>
       </c>
       <c r="B9" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137068280</v>
       </c>
       <c r="B10" t="n">
-        <v>92388</v>
+        <v>92389</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137068087</v>
       </c>
       <c r="B11" t="n">
-        <v>92113</v>
+        <v>92114</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137068042</v>
       </c>
       <c r="B12" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137068050</v>
       </c>
       <c r="B13" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137068055</v>
       </c>
       <c r="B14" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137068063</v>
       </c>
       <c r="B15" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137068069</v>
       </c>
       <c r="B16" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137068072</v>
       </c>
       <c r="B17" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137068073</v>
       </c>
       <c r="B18" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137068083</v>
       </c>
       <c r="B19" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137068088</v>
       </c>
       <c r="B20" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137068265</v>
       </c>
       <c r="B21" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137068270</v>
       </c>
       <c r="B22" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137068053</v>
       </c>
       <c r="B23" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137068263</v>
       </c>
       <c r="B24" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137068267</v>
       </c>
       <c r="B25" t="n">
-        <v>92549</v>
+        <v>92550</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>137068086</v>
       </c>
       <c r="B28" t="n">
-        <v>83349</v>
+        <v>83350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>137068039</v>
       </c>
       <c r="B30" t="n">
-        <v>92080</v>
+        <v>92081</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>137068025</v>
       </c>
       <c r="B33" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>137068028</v>
       </c>
       <c r="B34" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>137068037</v>
       </c>
       <c r="B35" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>137068044</v>
       </c>
       <c r="B36" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>137068049</v>
       </c>
       <c r="B37" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>137068051</v>
       </c>
       <c r="B38" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>137068057</v>
       </c>
       <c r="B39" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>137068064</v>
       </c>
       <c r="B40" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>137068065</v>
       </c>
       <c r="B41" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137068067</v>
       </c>
       <c r="B42" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>137068071</v>
       </c>
       <c r="B43" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>137068085</v>
       </c>
       <c r="B44" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>137068250</v>
       </c>
       <c r="B45" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>137068257</v>
       </c>
       <c r="B46" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>137068260</v>
       </c>
       <c r="B47" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>137068261</v>
       </c>
       <c r="B48" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>137068271</v>
       </c>
       <c r="B49" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>137068272</v>
       </c>
       <c r="B50" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>137068275</v>
       </c>
       <c r="B51" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>137068277</v>
       </c>
       <c r="B52" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>137068278</v>
       </c>
       <c r="B53" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137068279</v>
       </c>
       <c r="B54" t="n">
-        <v>79482</v>
+        <v>79483</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>137068036</v>
       </c>
       <c r="B61" t="n">
-        <v>83452</v>
+        <v>83453</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>137068027</v>
       </c>
       <c r="B62" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>137068038</v>
       </c>
       <c r="B63" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>137068056</v>
       </c>
       <c r="B64" t="n">
-        <v>83469</v>
+        <v>83470</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>137068045</v>
       </c>
       <c r="B74" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>137068068</v>
       </c>
       <c r="B75" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>137068076</v>
       </c>
       <c r="B76" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>137068255</v>
       </c>
       <c r="B77" t="n">
-        <v>80597</v>
+        <v>80598</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>137068032</v>
       </c>
       <c r="B78" t="n">
-        <v>79738</v>
+        <v>79739</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>137068041</v>
       </c>
       <c r="B79" t="n">
-        <v>79738</v>
+        <v>79739</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>137068070</v>
       </c>
       <c r="B80" t="n">
-        <v>79738</v>
+        <v>79739</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>137068084</v>
       </c>
       <c r="B81" t="n">
-        <v>79738</v>
+        <v>79739</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>137068048</v>
       </c>
       <c r="B82" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>137068256</v>
       </c>
       <c r="B83" t="n">
-        <v>80608</v>
+        <v>80609</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>137068031</v>
       </c>
       <c r="B84" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>137068047</v>
       </c>
       <c r="B85" t="n">
-        <v>80609</v>
+        <v>80610</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>137068082</v>
       </c>
       <c r="B104" t="n">
-        <v>99278</v>
+        <v>99279</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>137068030</v>
       </c>
       <c r="B105" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>137068066</v>
       </c>
       <c r="B106" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>137068093</v>
       </c>
       <c r="B107" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>137068243</v>
       </c>
       <c r="B108" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>137068259</v>
       </c>
       <c r="B109" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>137068273</v>
       </c>
       <c r="B110" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>137068043</v>
       </c>
       <c r="B111" t="n">
-        <v>110106</v>
+        <v>110107</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37165-2026 artfynd.xlsx
+++ b/artfynd/A 37165-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068262</v>
       </c>
       <c r="B2" t="n">
-        <v>92068</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137068264</v>
       </c>
       <c r="B3" t="n">
-        <v>92068</v>
+        <v>92074</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137068052</v>
       </c>
       <c r="B4" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137068074</v>
       </c>
       <c r="B5" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137068079</v>
       </c>
       <c r="B6" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137068089</v>
       </c>
       <c r="B7" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137068266</v>
       </c>
       <c r="B8" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137068268</v>
       </c>
       <c r="B9" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137068280</v>
       </c>
       <c r="B10" t="n">
-        <v>92389</v>
+        <v>92395</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137068087</v>
       </c>
       <c r="B11" t="n">
-        <v>92114</v>
+        <v>92120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137068042</v>
       </c>
       <c r="B12" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137068050</v>
       </c>
       <c r="B13" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137068055</v>
       </c>
       <c r="B14" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137068063</v>
       </c>
       <c r="B15" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137068069</v>
       </c>
       <c r="B16" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137068072</v>
       </c>
       <c r="B17" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137068073</v>
       </c>
       <c r="B18" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137068083</v>
       </c>
       <c r="B19" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137068088</v>
       </c>
       <c r="B20" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137068265</v>
       </c>
       <c r="B21" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137068270</v>
       </c>
       <c r="B22" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137068053</v>
       </c>
       <c r="B23" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137068263</v>
       </c>
       <c r="B24" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137068267</v>
       </c>
       <c r="B25" t="n">
-        <v>92550</v>
+        <v>92556</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>137068039</v>
       </c>
       <c r="B30" t="n">
-        <v>92081</v>
+        <v>92087</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>137068082</v>
       </c>
       <c r="B104" t="n">
-        <v>99279</v>
+        <v>99285</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>137068030</v>
       </c>
       <c r="B105" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>137068066</v>
       </c>
       <c r="B106" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>137068093</v>
       </c>
       <c r="B107" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>137068243</v>
       </c>
       <c r="B108" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>137068259</v>
       </c>
       <c r="B109" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>137068273</v>
       </c>
       <c r="B110" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>137068043</v>
       </c>
       <c r="B111" t="n">
-        <v>110107</v>
+        <v>110113</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37165-2026 artfynd.xlsx
+++ b/artfynd/A 37165-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068262</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92078</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137068264</v>
       </c>
       <c r="B3" t="n">
-        <v>92074</v>
+        <v>92078</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137068052</v>
       </c>
       <c r="B4" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137068074</v>
       </c>
       <c r="B5" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137068079</v>
       </c>
       <c r="B6" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137068089</v>
       </c>
       <c r="B7" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137068266</v>
       </c>
       <c r="B8" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137068268</v>
       </c>
       <c r="B9" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137068280</v>
       </c>
       <c r="B10" t="n">
-        <v>92395</v>
+        <v>92399</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137068087</v>
       </c>
       <c r="B11" t="n">
-        <v>92120</v>
+        <v>92124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137068042</v>
       </c>
       <c r="B12" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137068050</v>
       </c>
       <c r="B13" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137068055</v>
       </c>
       <c r="B14" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137068063</v>
       </c>
       <c r="B15" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137068069</v>
       </c>
       <c r="B16" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137068072</v>
       </c>
       <c r="B17" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137068073</v>
       </c>
       <c r="B18" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137068083</v>
       </c>
       <c r="B19" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137068088</v>
       </c>
       <c r="B20" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137068265</v>
       </c>
       <c r="B21" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137068270</v>
       </c>
       <c r="B22" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137068053</v>
       </c>
       <c r="B23" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137068263</v>
       </c>
       <c r="B24" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137068267</v>
       </c>
       <c r="B25" t="n">
-        <v>92556</v>
+        <v>92560</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>137068086</v>
       </c>
       <c r="B28" t="n">
-        <v>83350</v>
+        <v>83354</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>137068039</v>
       </c>
       <c r="B30" t="n">
-        <v>92087</v>
+        <v>92091</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>137068025</v>
       </c>
       <c r="B33" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>137068028</v>
       </c>
       <c r="B34" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>137068037</v>
       </c>
       <c r="B35" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>137068044</v>
       </c>
       <c r="B36" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>137068049</v>
       </c>
       <c r="B37" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>137068051</v>
       </c>
       <c r="B38" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>137068057</v>
       </c>
       <c r="B39" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>137068064</v>
       </c>
       <c r="B40" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>137068065</v>
       </c>
       <c r="B41" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137068067</v>
       </c>
       <c r="B42" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>137068071</v>
       </c>
       <c r="B43" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>137068085</v>
       </c>
       <c r="B44" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>137068250</v>
       </c>
       <c r="B45" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>137068257</v>
       </c>
       <c r="B46" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>137068260</v>
       </c>
       <c r="B47" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>137068261</v>
       </c>
       <c r="B48" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>137068271</v>
       </c>
       <c r="B49" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>137068272</v>
       </c>
       <c r="B50" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>137068275</v>
       </c>
       <c r="B51" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>137068277</v>
       </c>
       <c r="B52" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>137068278</v>
       </c>
       <c r="B53" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137068279</v>
       </c>
       <c r="B54" t="n">
-        <v>79483</v>
+        <v>79485</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>137068036</v>
       </c>
       <c r="B61" t="n">
-        <v>83453</v>
+        <v>83457</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>137068027</v>
       </c>
       <c r="B62" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>137068038</v>
       </c>
       <c r="B63" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>137068056</v>
       </c>
       <c r="B64" t="n">
-        <v>83470</v>
+        <v>83474</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>137068045</v>
       </c>
       <c r="B74" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>137068068</v>
       </c>
       <c r="B75" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>137068076</v>
       </c>
       <c r="B76" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>137068255</v>
       </c>
       <c r="B77" t="n">
-        <v>80598</v>
+        <v>80600</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>137068032</v>
       </c>
       <c r="B78" t="n">
-        <v>79739</v>
+        <v>79741</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>137068041</v>
       </c>
       <c r="B79" t="n">
-        <v>79739</v>
+        <v>79741</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>137068070</v>
       </c>
       <c r="B80" t="n">
-        <v>79739</v>
+        <v>79741</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>137068084</v>
       </c>
       <c r="B81" t="n">
-        <v>79739</v>
+        <v>79741</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>137068048</v>
       </c>
       <c r="B82" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>137068256</v>
       </c>
       <c r="B83" t="n">
-        <v>80609</v>
+        <v>80611</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>137068031</v>
       </c>
       <c r="B84" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>137068047</v>
       </c>
       <c r="B85" t="n">
-        <v>80610</v>
+        <v>80612</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>137068082</v>
       </c>
       <c r="B104" t="n">
-        <v>99285</v>
+        <v>99289</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>137068030</v>
       </c>
       <c r="B105" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>137068066</v>
       </c>
       <c r="B106" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>137068093</v>
       </c>
       <c r="B107" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>137068243</v>
       </c>
       <c r="B108" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>137068259</v>
       </c>
       <c r="B109" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>137068273</v>
       </c>
       <c r="B110" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>137068043</v>
       </c>
       <c r="B111" t="n">
-        <v>110113</v>
+        <v>110117</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37165-2026 artfynd.xlsx
+++ b/artfynd/A 37165-2026 artfynd.xlsx
@@ -12077,7 +12077,7 @@
         <v>137068082</v>
       </c>
       <c r="B104" t="n">
-        <v>99289</v>
+        <v>99291</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>137068030</v>
       </c>
       <c r="B105" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>137068066</v>
       </c>
       <c r="B106" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>137068093</v>
       </c>
       <c r="B107" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>137068243</v>
       </c>
       <c r="B108" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>137068259</v>
       </c>
       <c r="B109" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>137068273</v>
       </c>
       <c r="B110" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>137068043</v>
       </c>
       <c r="B111" t="n">
-        <v>110117</v>
+        <v>110119</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37165-2026 artfynd.xlsx
+++ b/artfynd/A 37165-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068262</v>
       </c>
       <c r="B2" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137068264</v>
       </c>
       <c r="B3" t="n">
-        <v>92078</v>
+        <v>92080</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137068052</v>
       </c>
       <c r="B4" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137068074</v>
       </c>
       <c r="B5" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137068079</v>
       </c>
       <c r="B6" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137068089</v>
       </c>
       <c r="B7" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137068266</v>
       </c>
       <c r="B8" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137068268</v>
       </c>
       <c r="B9" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137068280</v>
       </c>
       <c r="B10" t="n">
-        <v>92399</v>
+        <v>92401</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137068087</v>
       </c>
       <c r="B11" t="n">
-        <v>92124</v>
+        <v>92126</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137068042</v>
       </c>
       <c r="B12" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137068050</v>
       </c>
       <c r="B13" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137068055</v>
       </c>
       <c r="B14" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137068063</v>
       </c>
       <c r="B15" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137068069</v>
       </c>
       <c r="B16" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137068072</v>
       </c>
       <c r="B17" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137068073</v>
       </c>
       <c r="B18" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137068083</v>
       </c>
       <c r="B19" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137068088</v>
       </c>
       <c r="B20" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137068265</v>
       </c>
       <c r="B21" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137068270</v>
       </c>
       <c r="B22" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137068053</v>
       </c>
       <c r="B23" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137068263</v>
       </c>
       <c r="B24" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137068267</v>
       </c>
       <c r="B25" t="n">
-        <v>92560</v>
+        <v>92562</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>137068086</v>
       </c>
       <c r="B28" t="n">
-        <v>83354</v>
+        <v>83356</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>137068039</v>
       </c>
       <c r="B30" t="n">
-        <v>92091</v>
+        <v>92093</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>137068025</v>
       </c>
       <c r="B33" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>137068028</v>
       </c>
       <c r="B34" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>137068037</v>
       </c>
       <c r="B35" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>137068044</v>
       </c>
       <c r="B36" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>137068049</v>
       </c>
       <c r="B37" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>137068051</v>
       </c>
       <c r="B38" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>137068057</v>
       </c>
       <c r="B39" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>137068064</v>
       </c>
       <c r="B40" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>137068065</v>
       </c>
       <c r="B41" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137068067</v>
       </c>
       <c r="B42" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>137068071</v>
       </c>
       <c r="B43" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>137068085</v>
       </c>
       <c r="B44" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>137068250</v>
       </c>
       <c r="B45" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>137068257</v>
       </c>
       <c r="B46" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>137068260</v>
       </c>
       <c r="B47" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>137068261</v>
       </c>
       <c r="B48" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>137068271</v>
       </c>
       <c r="B49" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>137068272</v>
       </c>
       <c r="B50" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>137068275</v>
       </c>
       <c r="B51" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>137068277</v>
       </c>
       <c r="B52" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>137068278</v>
       </c>
       <c r="B53" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137068279</v>
       </c>
       <c r="B54" t="n">
-        <v>79485</v>
+        <v>79488</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>137068036</v>
       </c>
       <c r="B61" t="n">
-        <v>83457</v>
+        <v>83459</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>137068027</v>
       </c>
       <c r="B62" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>137068038</v>
       </c>
       <c r="B63" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>137068056</v>
       </c>
       <c r="B64" t="n">
-        <v>83474</v>
+        <v>83476</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>137068045</v>
       </c>
       <c r="B74" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>137068068</v>
       </c>
       <c r="B75" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>137068076</v>
       </c>
       <c r="B76" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>137068255</v>
       </c>
       <c r="B77" t="n">
-        <v>80600</v>
+        <v>80603</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>137068032</v>
       </c>
       <c r="B78" t="n">
-        <v>79741</v>
+        <v>79744</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>137068041</v>
       </c>
       <c r="B79" t="n">
-        <v>79741</v>
+        <v>79744</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>137068070</v>
       </c>
       <c r="B80" t="n">
-        <v>79741</v>
+        <v>79744</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>137068084</v>
       </c>
       <c r="B81" t="n">
-        <v>79741</v>
+        <v>79744</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>137068048</v>
       </c>
       <c r="B82" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>137068256</v>
       </c>
       <c r="B83" t="n">
-        <v>80611</v>
+        <v>80614</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>137068031</v>
       </c>
       <c r="B84" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>137068047</v>
       </c>
       <c r="B85" t="n">
-        <v>80612</v>
+        <v>80615</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>137068082</v>
       </c>
       <c r="B104" t="n">
-        <v>99291</v>
+        <v>99293</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>137068030</v>
       </c>
       <c r="B105" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>137068066</v>
       </c>
       <c r="B106" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>137068093</v>
       </c>
       <c r="B107" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>137068243</v>
       </c>
       <c r="B108" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>137068259</v>
       </c>
       <c r="B109" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>137068273</v>
       </c>
       <c r="B110" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>137068043</v>
       </c>
       <c r="B111" t="n">
-        <v>110119</v>
+        <v>110121</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37165-2026 artfynd.xlsx
+++ b/artfynd/A 37165-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068262</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92093</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137068264</v>
       </c>
       <c r="B3" t="n">
-        <v>92080</v>
+        <v>92093</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137068052</v>
       </c>
       <c r="B4" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137068074</v>
       </c>
       <c r="B5" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137068079</v>
       </c>
       <c r="B6" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137068089</v>
       </c>
       <c r="B7" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137068266</v>
       </c>
       <c r="B8" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137068268</v>
       </c>
       <c r="B9" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137068280</v>
       </c>
       <c r="B10" t="n">
-        <v>92401</v>
+        <v>92414</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137068087</v>
       </c>
       <c r="B11" t="n">
-        <v>92126</v>
+        <v>92139</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137068042</v>
       </c>
       <c r="B12" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137068050</v>
       </c>
       <c r="B13" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137068055</v>
       </c>
       <c r="B14" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137068063</v>
       </c>
       <c r="B15" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137068069</v>
       </c>
       <c r="B16" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137068072</v>
       </c>
       <c r="B17" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137068073</v>
       </c>
       <c r="B18" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137068083</v>
       </c>
       <c r="B19" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137068088</v>
       </c>
       <c r="B20" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137068265</v>
       </c>
       <c r="B21" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137068270</v>
       </c>
       <c r="B22" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137068053</v>
       </c>
       <c r="B23" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137068263</v>
       </c>
       <c r="B24" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137068267</v>
       </c>
       <c r="B25" t="n">
-        <v>92562</v>
+        <v>92575</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>137068086</v>
       </c>
       <c r="B28" t="n">
-        <v>83356</v>
+        <v>83369</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>137068039</v>
       </c>
       <c r="B30" t="n">
-        <v>92093</v>
+        <v>92106</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>137068025</v>
       </c>
       <c r="B33" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>137068028</v>
       </c>
       <c r="B34" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>137068037</v>
       </c>
       <c r="B35" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>137068044</v>
       </c>
       <c r="B36" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>137068049</v>
       </c>
       <c r="B37" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>137068051</v>
       </c>
       <c r="B38" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>137068057</v>
       </c>
       <c r="B39" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>137068064</v>
       </c>
       <c r="B40" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>137068065</v>
       </c>
       <c r="B41" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137068067</v>
       </c>
       <c r="B42" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>137068071</v>
       </c>
       <c r="B43" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>137068085</v>
       </c>
       <c r="B44" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>137068250</v>
       </c>
       <c r="B45" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>137068257</v>
       </c>
       <c r="B46" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>137068260</v>
       </c>
       <c r="B47" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>137068261</v>
       </c>
       <c r="B48" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>137068271</v>
       </c>
       <c r="B49" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>137068272</v>
       </c>
       <c r="B50" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>137068275</v>
       </c>
       <c r="B51" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>137068277</v>
       </c>
       <c r="B52" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>137068278</v>
       </c>
       <c r="B53" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137068279</v>
       </c>
       <c r="B54" t="n">
-        <v>79488</v>
+        <v>79501</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>137068029</v>
       </c>
       <c r="B55" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>137068033</v>
       </c>
       <c r="B56" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>137068034</v>
       </c>
       <c r="B57" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>137068035</v>
       </c>
       <c r="B58" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>137068252</v>
       </c>
       <c r="B59" t="n">
-        <v>75566</v>
+        <v>75579</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>137068036</v>
       </c>
       <c r="B61" t="n">
-        <v>83459</v>
+        <v>83472</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>137068027</v>
       </c>
       <c r="B62" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>137068038</v>
       </c>
       <c r="B63" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>137068056</v>
       </c>
       <c r="B64" t="n">
-        <v>83476</v>
+        <v>83489</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>137068045</v>
       </c>
       <c r="B74" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>137068068</v>
       </c>
       <c r="B75" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>137068076</v>
       </c>
       <c r="B76" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>137068255</v>
       </c>
       <c r="B77" t="n">
-        <v>80603</v>
+        <v>80616</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>137068032</v>
       </c>
       <c r="B78" t="n">
-        <v>79744</v>
+        <v>79757</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>137068041</v>
       </c>
       <c r="B79" t="n">
-        <v>79744</v>
+        <v>79757</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>137068070</v>
       </c>
       <c r="B80" t="n">
-        <v>79744</v>
+        <v>79757</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>137068084</v>
       </c>
       <c r="B81" t="n">
-        <v>79744</v>
+        <v>79757</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>137068048</v>
       </c>
       <c r="B82" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>137068256</v>
       </c>
       <c r="B83" t="n">
-        <v>80614</v>
+        <v>80627</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>137068031</v>
       </c>
       <c r="B84" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>137068047</v>
       </c>
       <c r="B85" t="n">
-        <v>80615</v>
+        <v>80628</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>137068054</v>
       </c>
       <c r="B86" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>137068060</v>
       </c>
       <c r="B87" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>137068061</v>
       </c>
       <c r="B88" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>137068062</v>
       </c>
       <c r="B89" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>137068077</v>
       </c>
       <c r="B90" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>137068080</v>
       </c>
       <c r="B91" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>137068081</v>
       </c>
       <c r="B92" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>137068090</v>
       </c>
       <c r="B93" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>137068092</v>
       </c>
       <c r="B94" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>137068245</v>
       </c>
       <c r="B95" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>137068248</v>
       </c>
       <c r="B96" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>137068253</v>
       </c>
       <c r="B97" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>137068258</v>
       </c>
       <c r="B98" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>137068274</v>
       </c>
       <c r="B99" t="n">
-        <v>58008</v>
+        <v>58021</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>137068058</v>
       </c>
       <c r="B101" t="n">
-        <v>57186</v>
+        <v>57199</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>81135642</v>
       </c>
       <c r="B102" t="n">
-        <v>58112</v>
+        <v>58125</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>137068082</v>
       </c>
       <c r="B104" t="n">
-        <v>99293</v>
+        <v>99306</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>137068030</v>
       </c>
       <c r="B105" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>137068066</v>
       </c>
       <c r="B106" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>137068093</v>
       </c>
       <c r="B107" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>137068243</v>
       </c>
       <c r="B108" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>137068259</v>
       </c>
       <c r="B109" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>137068273</v>
       </c>
       <c r="B110" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>137068043</v>
       </c>
       <c r="B111" t="n">
-        <v>110121</v>
+        <v>110134</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37165-2026 artfynd.xlsx
+++ b/artfynd/A 37165-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068262</v>
       </c>
       <c r="B2" t="n">
-        <v>92093</v>
+        <v>92095</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137068264</v>
       </c>
       <c r="B3" t="n">
-        <v>92093</v>
+        <v>92095</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137068052</v>
       </c>
       <c r="B4" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137068074</v>
       </c>
       <c r="B5" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137068079</v>
       </c>
       <c r="B6" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137068089</v>
       </c>
       <c r="B7" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137068266</v>
       </c>
       <c r="B8" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137068268</v>
       </c>
       <c r="B9" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137068280</v>
       </c>
       <c r="B10" t="n">
-        <v>92414</v>
+        <v>92416</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137068087</v>
       </c>
       <c r="B11" t="n">
-        <v>92139</v>
+        <v>92141</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137068042</v>
       </c>
       <c r="B12" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137068050</v>
       </c>
       <c r="B13" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137068055</v>
       </c>
       <c r="B14" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137068063</v>
       </c>
       <c r="B15" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137068069</v>
       </c>
       <c r="B16" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137068072</v>
       </c>
       <c r="B17" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137068073</v>
       </c>
       <c r="B18" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137068083</v>
       </c>
       <c r="B19" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137068088</v>
       </c>
       <c r="B20" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137068265</v>
       </c>
       <c r="B21" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137068270</v>
       </c>
       <c r="B22" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137068053</v>
       </c>
       <c r="B23" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137068263</v>
       </c>
       <c r="B24" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137068267</v>
       </c>
       <c r="B25" t="n">
-        <v>92575</v>
+        <v>92577</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>137068086</v>
       </c>
       <c r="B28" t="n">
-        <v>83369</v>
+        <v>83371</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>137068039</v>
       </c>
       <c r="B30" t="n">
-        <v>92106</v>
+        <v>92108</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>137068025</v>
       </c>
       <c r="B33" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>137068028</v>
       </c>
       <c r="B34" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>137068037</v>
       </c>
       <c r="B35" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>137068044</v>
       </c>
       <c r="B36" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>137068049</v>
       </c>
       <c r="B37" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>137068051</v>
       </c>
       <c r="B38" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>137068057</v>
       </c>
       <c r="B39" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>137068064</v>
       </c>
       <c r="B40" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>137068065</v>
       </c>
       <c r="B41" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137068067</v>
       </c>
       <c r="B42" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>137068071</v>
       </c>
       <c r="B43" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>137068085</v>
       </c>
       <c r="B44" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>137068250</v>
       </c>
       <c r="B45" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>137068257</v>
       </c>
       <c r="B46" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>137068260</v>
       </c>
       <c r="B47" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>137068261</v>
       </c>
       <c r="B48" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>137068271</v>
       </c>
       <c r="B49" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>137068272</v>
       </c>
       <c r="B50" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>137068275</v>
       </c>
       <c r="B51" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>137068277</v>
       </c>
       <c r="B52" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>137068278</v>
       </c>
       <c r="B53" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137068279</v>
       </c>
       <c r="B54" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>137068029</v>
       </c>
       <c r="B55" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>137068033</v>
       </c>
       <c r="B56" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>137068034</v>
       </c>
       <c r="B57" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>137068035</v>
       </c>
       <c r="B58" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>137068252</v>
       </c>
       <c r="B59" t="n">
-        <v>75579</v>
+        <v>75581</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>137068036</v>
       </c>
       <c r="B61" t="n">
-        <v>83472</v>
+        <v>83474</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>137068027</v>
       </c>
       <c r="B62" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>137068038</v>
       </c>
       <c r="B63" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>137068056</v>
       </c>
       <c r="B64" t="n">
-        <v>83489</v>
+        <v>83491</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>137068045</v>
       </c>
       <c r="B74" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>137068068</v>
       </c>
       <c r="B75" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>137068076</v>
       </c>
       <c r="B76" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>137068255</v>
       </c>
       <c r="B77" t="n">
-        <v>80616</v>
+        <v>80618</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>137068032</v>
       </c>
       <c r="B78" t="n">
-        <v>79757</v>
+        <v>79759</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>137068041</v>
       </c>
       <c r="B79" t="n">
-        <v>79757</v>
+        <v>79759</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>137068070</v>
       </c>
       <c r="B80" t="n">
-        <v>79757</v>
+        <v>79759</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>137068084</v>
       </c>
       <c r="B81" t="n">
-        <v>79757</v>
+        <v>79759</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>137068048</v>
       </c>
       <c r="B82" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>137068256</v>
       </c>
       <c r="B83" t="n">
-        <v>80627</v>
+        <v>80629</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>137068031</v>
       </c>
       <c r="B84" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>137068047</v>
       </c>
       <c r="B85" t="n">
-        <v>80628</v>
+        <v>80630</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>137068054</v>
       </c>
       <c r="B86" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10064,7 +10064,7 @@
         <v>137068060</v>
       </c>
       <c r="B87" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10186,7 +10186,7 @@
         <v>137068061</v>
       </c>
       <c r="B88" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10308,7 +10308,7 @@
         <v>137068062</v>
       </c>
       <c r="B89" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10430,7 +10430,7 @@
         <v>137068077</v>
       </c>
       <c r="B90" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
         <v>137068080</v>
       </c>
       <c r="B91" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10674,7 +10674,7 @@
         <v>137068081</v>
       </c>
       <c r="B92" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10796,7 +10796,7 @@
         <v>137068090</v>
       </c>
       <c r="B93" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10918,7 +10918,7 @@
         <v>137068092</v>
       </c>
       <c r="B94" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11040,7 +11040,7 @@
         <v>137068245</v>
       </c>
       <c r="B95" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11162,7 +11162,7 @@
         <v>137068248</v>
       </c>
       <c r="B96" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>137068253</v>
       </c>
       <c r="B97" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11406,7 +11406,7 @@
         <v>137068258</v>
       </c>
       <c r="B98" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11528,7 +11528,7 @@
         <v>137068274</v>
       </c>
       <c r="B99" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11752,7 +11752,7 @@
         <v>137068058</v>
       </c>
       <c r="B101" t="n">
-        <v>57199</v>
+        <v>57201</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11873,7 +11873,7 @@
         <v>81135642</v>
       </c>
       <c r="B102" t="n">
-        <v>58125</v>
+        <v>58127</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12077,7 +12077,7 @@
         <v>137068082</v>
       </c>
       <c r="B104" t="n">
-        <v>99306</v>
+        <v>99308</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12189,7 +12189,7 @@
         <v>137068030</v>
       </c>
       <c r="B105" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12310,7 +12310,7 @@
         <v>137068066</v>
       </c>
       <c r="B106" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12431,7 +12431,7 @@
         <v>137068093</v>
       </c>
       <c r="B107" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12552,7 +12552,7 @@
         <v>137068243</v>
       </c>
       <c r="B108" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12669,7 +12669,7 @@
         <v>137068259</v>
       </c>
       <c r="B109" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12786,7 +12786,7 @@
         <v>137068273</v>
       </c>
       <c r="B110" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12903,7 +12903,7 @@
         <v>137068043</v>
       </c>
       <c r="B111" t="n">
-        <v>110134</v>
+        <v>110136</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37165-2026 artfynd.xlsx
+++ b/artfynd/A 37165-2026 artfynd.xlsx
@@ -9968,11 +9968,7 @@
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
           <t>Matsäckbacken, Mpd</t>
@@ -10090,11 +10086,7 @@
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Matsäckbacken, Mpd</t>
@@ -10212,11 +10204,7 @@
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Matsäckbacken, Mpd</t>
@@ -10334,11 +10322,7 @@
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Matsäckbacken, Mpd</t>
@@ -10456,11 +10440,7 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Matsäckbacken, Mpd</t>
@@ -10578,11 +10558,7 @@
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Matsäckbacken, Mpd</t>
@@ -10700,11 +10676,7 @@
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Matsäckbacken, Mpd</t>
@@ -10822,11 +10794,7 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
-      <c r="M93" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
           <t>Matsäckbacken, Mpd</t>
@@ -10944,11 +10912,7 @@
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Matsäckbacken, Mpd</t>
@@ -11066,11 +11030,7 @@
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Matsäckbacken, Mpd</t>
@@ -11188,11 +11148,7 @@
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="M96" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
           <t>Matsäckbacken, Mpd</t>
@@ -11310,11 +11266,7 @@
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Matsäckbacken, Mpd</t>
@@ -11432,11 +11384,7 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
           <t>Matsäckbacken, Mpd</t>
@@ -11554,11 +11502,7 @@
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
           <t>Matsäckbacken, Mpd</t>
@@ -11782,11 +11726,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
           <t>Matsäckbacken, Mpd</t>

--- a/artfynd/A 37165-2026 artfynd.xlsx
+++ b/artfynd/A 37165-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068262</v>
       </c>
       <c r="B2" t="n">
-        <v>92095</v>
+        <v>92098</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137068264</v>
       </c>
       <c r="B3" t="n">
-        <v>92095</v>
+        <v>92098</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137068052</v>
       </c>
       <c r="B4" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137068074</v>
       </c>
       <c r="B5" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137068079</v>
       </c>
       <c r="B6" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137068089</v>
       </c>
       <c r="B7" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137068266</v>
       </c>
       <c r="B8" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137068268</v>
       </c>
       <c r="B9" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137068280</v>
       </c>
       <c r="B10" t="n">
-        <v>92416</v>
+        <v>92419</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137068087</v>
       </c>
       <c r="B11" t="n">
-        <v>92141</v>
+        <v>92144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137068042</v>
       </c>
       <c r="B12" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137068050</v>
       </c>
       <c r="B13" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137068055</v>
       </c>
       <c r="B14" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137068063</v>
       </c>
       <c r="B15" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137068069</v>
       </c>
       <c r="B16" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137068072</v>
       </c>
       <c r="B17" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137068073</v>
       </c>
       <c r="B18" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137068083</v>
       </c>
       <c r="B19" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137068088</v>
       </c>
       <c r="B20" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137068265</v>
       </c>
       <c r="B21" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137068270</v>
       </c>
       <c r="B22" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137068053</v>
       </c>
       <c r="B23" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137068263</v>
       </c>
       <c r="B24" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137068267</v>
       </c>
       <c r="B25" t="n">
-        <v>92577</v>
+        <v>92580</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>137068039</v>
       </c>
       <c r="B30" t="n">
-        <v>92108</v>
+        <v>92111</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>137068036</v>
       </c>
       <c r="B61" t="n">
-        <v>83474</v>
+        <v>83477</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>137068027</v>
       </c>
       <c r="B62" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>137068038</v>
       </c>
       <c r="B63" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>137068056</v>
       </c>
       <c r="B64" t="n">
-        <v>83491</v>
+        <v>83494</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>137068082</v>
       </c>
       <c r="B104" t="n">
-        <v>99308</v>
+        <v>99311</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>137068030</v>
       </c>
       <c r="B105" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>137068066</v>
       </c>
       <c r="B106" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>137068093</v>
       </c>
       <c r="B107" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>137068243</v>
       </c>
       <c r="B108" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>137068259</v>
       </c>
       <c r="B109" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>137068273</v>
       </c>
       <c r="B110" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>137068043</v>
       </c>
       <c r="B111" t="n">
-        <v>110136</v>
+        <v>110141</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37165-2026 artfynd.xlsx
+++ b/artfynd/A 37165-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068262</v>
       </c>
       <c r="B2" t="n">
-        <v>92098</v>
+        <v>92108</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137068264</v>
       </c>
       <c r="B3" t="n">
-        <v>92098</v>
+        <v>92108</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137068052</v>
       </c>
       <c r="B4" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137068074</v>
       </c>
       <c r="B5" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137068079</v>
       </c>
       <c r="B6" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137068089</v>
       </c>
       <c r="B7" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137068266</v>
       </c>
       <c r="B8" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137068268</v>
       </c>
       <c r="B9" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137068280</v>
       </c>
       <c r="B10" t="n">
-        <v>92419</v>
+        <v>92429</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137068087</v>
       </c>
       <c r="B11" t="n">
-        <v>92144</v>
+        <v>92154</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137068042</v>
       </c>
       <c r="B12" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137068050</v>
       </c>
       <c r="B13" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137068055</v>
       </c>
       <c r="B14" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137068063</v>
       </c>
       <c r="B15" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137068069</v>
       </c>
       <c r="B16" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137068072</v>
       </c>
       <c r="B17" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137068073</v>
       </c>
       <c r="B18" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137068083</v>
       </c>
       <c r="B19" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137068088</v>
       </c>
       <c r="B20" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137068265</v>
       </c>
       <c r="B21" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137068270</v>
       </c>
       <c r="B22" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137068053</v>
       </c>
       <c r="B23" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137068263</v>
       </c>
       <c r="B24" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137068267</v>
       </c>
       <c r="B25" t="n">
-        <v>92580</v>
+        <v>92590</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>137068086</v>
       </c>
       <c r="B28" t="n">
-        <v>83371</v>
+        <v>83381</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>137068039</v>
       </c>
       <c r="B30" t="n">
-        <v>92111</v>
+        <v>92121</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>137068025</v>
       </c>
       <c r="B33" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>137068028</v>
       </c>
       <c r="B34" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>137068037</v>
       </c>
       <c r="B35" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>137068044</v>
       </c>
       <c r="B36" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>137068049</v>
       </c>
       <c r="B37" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>137068051</v>
       </c>
       <c r="B38" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>137068057</v>
       </c>
       <c r="B39" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>137068064</v>
       </c>
       <c r="B40" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>137068065</v>
       </c>
       <c r="B41" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137068067</v>
       </c>
       <c r="B42" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>137068071</v>
       </c>
       <c r="B43" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>137068085</v>
       </c>
       <c r="B44" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>137068250</v>
       </c>
       <c r="B45" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>137068257</v>
       </c>
       <c r="B46" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>137068260</v>
       </c>
       <c r="B47" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>137068261</v>
       </c>
       <c r="B48" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>137068271</v>
       </c>
       <c r="B49" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>137068272</v>
       </c>
       <c r="B50" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>137068275</v>
       </c>
       <c r="B51" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>137068277</v>
       </c>
       <c r="B52" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>137068278</v>
       </c>
       <c r="B53" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137068279</v>
       </c>
       <c r="B54" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>137068029</v>
       </c>
       <c r="B55" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>137068033</v>
       </c>
       <c r="B56" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>137068034</v>
       </c>
       <c r="B57" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>137068035</v>
       </c>
       <c r="B58" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>137068252</v>
       </c>
       <c r="B59" t="n">
-        <v>75581</v>
+        <v>75591</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>137068036</v>
       </c>
       <c r="B61" t="n">
-        <v>83477</v>
+        <v>83487</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>137068027</v>
       </c>
       <c r="B62" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>137068038</v>
       </c>
       <c r="B63" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>137068056</v>
       </c>
       <c r="B64" t="n">
-        <v>83494</v>
+        <v>83504</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>137068045</v>
       </c>
       <c r="B74" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>137068068</v>
       </c>
       <c r="B75" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>137068076</v>
       </c>
       <c r="B76" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>137068255</v>
       </c>
       <c r="B77" t="n">
-        <v>80618</v>
+        <v>80628</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>137068032</v>
       </c>
       <c r="B78" t="n">
-        <v>79759</v>
+        <v>79769</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>137068041</v>
       </c>
       <c r="B79" t="n">
-        <v>79759</v>
+        <v>79769</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>137068070</v>
       </c>
       <c r="B80" t="n">
-        <v>79759</v>
+        <v>79769</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>137068084</v>
       </c>
       <c r="B81" t="n">
-        <v>79759</v>
+        <v>79769</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>137068048</v>
       </c>
       <c r="B82" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>137068256</v>
       </c>
       <c r="B83" t="n">
-        <v>80629</v>
+        <v>80639</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>137068031</v>
       </c>
       <c r="B84" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>137068047</v>
       </c>
       <c r="B85" t="n">
-        <v>80630</v>
+        <v>80640</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>137068054</v>
       </c>
       <c r="B86" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>137068060</v>
       </c>
       <c r="B87" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>137068061</v>
       </c>
       <c r="B88" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>137068062</v>
       </c>
       <c r="B89" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>137068077</v>
       </c>
       <c r="B90" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>137068080</v>
       </c>
       <c r="B91" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>137068081</v>
       </c>
       <c r="B92" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>137068090</v>
       </c>
       <c r="B93" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>137068092</v>
       </c>
       <c r="B94" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>137068245</v>
       </c>
       <c r="B95" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>137068248</v>
       </c>
       <c r="B96" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>137068253</v>
       </c>
       <c r="B97" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>137068258</v>
       </c>
       <c r="B98" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>137068274</v>
       </c>
       <c r="B99" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>137068058</v>
       </c>
       <c r="B101" t="n">
-        <v>57201</v>
+        <v>57211</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>137068082</v>
       </c>
       <c r="B104" t="n">
-        <v>99311</v>
+        <v>99321</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>137068030</v>
       </c>
       <c r="B105" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>137068066</v>
       </c>
       <c r="B106" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>137068093</v>
       </c>
       <c r="B107" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>137068243</v>
       </c>
       <c r="B108" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>137068259</v>
       </c>
       <c r="B109" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>137068273</v>
       </c>
       <c r="B110" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>137068043</v>
       </c>
       <c r="B111" t="n">
-        <v>110141</v>
+        <v>110162</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37165-2026 artfynd.xlsx
+++ b/artfynd/A 37165-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068262</v>
       </c>
       <c r="B2" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137068264</v>
       </c>
       <c r="B3" t="n">
-        <v>92108</v>
+        <v>92109</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137068052</v>
       </c>
       <c r="B4" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137068074</v>
       </c>
       <c r="B5" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137068079</v>
       </c>
       <c r="B6" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137068089</v>
       </c>
       <c r="B7" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137068266</v>
       </c>
       <c r="B8" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137068268</v>
       </c>
       <c r="B9" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137068280</v>
       </c>
       <c r="B10" t="n">
-        <v>92429</v>
+        <v>92430</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137068087</v>
       </c>
       <c r="B11" t="n">
-        <v>92154</v>
+        <v>92155</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137068042</v>
       </c>
       <c r="B12" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137068050</v>
       </c>
       <c r="B13" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137068055</v>
       </c>
       <c r="B14" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137068063</v>
       </c>
       <c r="B15" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137068069</v>
       </c>
       <c r="B16" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137068072</v>
       </c>
       <c r="B17" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137068073</v>
       </c>
       <c r="B18" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137068083</v>
       </c>
       <c r="B19" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137068088</v>
       </c>
       <c r="B20" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137068265</v>
       </c>
       <c r="B21" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137068270</v>
       </c>
       <c r="B22" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137068053</v>
       </c>
       <c r="B23" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137068263</v>
       </c>
       <c r="B24" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137068267</v>
       </c>
       <c r="B25" t="n">
-        <v>92590</v>
+        <v>92591</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>137068039</v>
       </c>
       <c r="B30" t="n">
-        <v>92121</v>
+        <v>92122</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>137068082</v>
       </c>
       <c r="B104" t="n">
-        <v>99321</v>
+        <v>99322</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>137068030</v>
       </c>
       <c r="B105" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>137068066</v>
       </c>
       <c r="B106" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>137068093</v>
       </c>
       <c r="B107" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>137068243</v>
       </c>
       <c r="B108" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>137068259</v>
       </c>
       <c r="B109" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>137068273</v>
       </c>
       <c r="B110" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>137068043</v>
       </c>
       <c r="B111" t="n">
-        <v>110162</v>
+        <v>110163</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37165-2026 artfynd.xlsx
+++ b/artfynd/A 37165-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068262</v>
       </c>
       <c r="B2" t="n">
-        <v>92109</v>
+        <v>92112</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137068264</v>
       </c>
       <c r="B3" t="n">
-        <v>92109</v>
+        <v>92112</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137068052</v>
       </c>
       <c r="B4" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137068074</v>
       </c>
       <c r="B5" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137068079</v>
       </c>
       <c r="B6" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137068089</v>
       </c>
       <c r="B7" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137068266</v>
       </c>
       <c r="B8" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137068268</v>
       </c>
       <c r="B9" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137068280</v>
       </c>
       <c r="B10" t="n">
-        <v>92430</v>
+        <v>92433</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137068087</v>
       </c>
       <c r="B11" t="n">
-        <v>92155</v>
+        <v>92158</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137068042</v>
       </c>
       <c r="B12" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137068050</v>
       </c>
       <c r="B13" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137068055</v>
       </c>
       <c r="B14" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137068063</v>
       </c>
       <c r="B15" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137068069</v>
       </c>
       <c r="B16" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137068072</v>
       </c>
       <c r="B17" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137068073</v>
       </c>
       <c r="B18" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137068083</v>
       </c>
       <c r="B19" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137068088</v>
       </c>
       <c r="B20" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137068265</v>
       </c>
       <c r="B21" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137068270</v>
       </c>
       <c r="B22" t="n">
-        <v>92159</v>
+        <v>92162</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137068053</v>
       </c>
       <c r="B23" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137068263</v>
       </c>
       <c r="B24" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137068267</v>
       </c>
       <c r="B25" t="n">
-        <v>92591</v>
+        <v>92594</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>137068086</v>
       </c>
       <c r="B28" t="n">
-        <v>83381</v>
+        <v>83384</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>137068039</v>
       </c>
       <c r="B30" t="n">
-        <v>92122</v>
+        <v>92125</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>137068025</v>
       </c>
       <c r="B33" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>137068028</v>
       </c>
       <c r="B34" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>137068037</v>
       </c>
       <c r="B35" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>137068044</v>
       </c>
       <c r="B36" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>137068049</v>
       </c>
       <c r="B37" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>137068051</v>
       </c>
       <c r="B38" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>137068057</v>
       </c>
       <c r="B39" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>137068064</v>
       </c>
       <c r="B40" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>137068065</v>
       </c>
       <c r="B41" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137068067</v>
       </c>
       <c r="B42" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>137068071</v>
       </c>
       <c r="B43" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>137068085</v>
       </c>
       <c r="B44" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>137068250</v>
       </c>
       <c r="B45" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>137068257</v>
       </c>
       <c r="B46" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>137068260</v>
       </c>
       <c r="B47" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>137068261</v>
       </c>
       <c r="B48" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>137068271</v>
       </c>
       <c r="B49" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>137068272</v>
       </c>
       <c r="B50" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>137068275</v>
       </c>
       <c r="B51" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>137068277</v>
       </c>
       <c r="B52" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>137068278</v>
       </c>
       <c r="B53" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137068279</v>
       </c>
       <c r="B54" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>137068029</v>
       </c>
       <c r="B55" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>137068033</v>
       </c>
       <c r="B56" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>137068034</v>
       </c>
       <c r="B57" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>137068035</v>
       </c>
       <c r="B58" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>137068252</v>
       </c>
       <c r="B59" t="n">
-        <v>75591</v>
+        <v>75594</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>137068036</v>
       </c>
       <c r="B61" t="n">
-        <v>83487</v>
+        <v>83490</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>137068027</v>
       </c>
       <c r="B62" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>137068038</v>
       </c>
       <c r="B63" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>137068056</v>
       </c>
       <c r="B64" t="n">
-        <v>83504</v>
+        <v>83507</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>137068045</v>
       </c>
       <c r="B74" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>137068068</v>
       </c>
       <c r="B75" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>137068076</v>
       </c>
       <c r="B76" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>137068255</v>
       </c>
       <c r="B77" t="n">
-        <v>80628</v>
+        <v>80631</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>137068032</v>
       </c>
       <c r="B78" t="n">
-        <v>79769</v>
+        <v>79772</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>137068041</v>
       </c>
       <c r="B79" t="n">
-        <v>79769</v>
+        <v>79772</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>137068070</v>
       </c>
       <c r="B80" t="n">
-        <v>79769</v>
+        <v>79772</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>137068084</v>
       </c>
       <c r="B81" t="n">
-        <v>79769</v>
+        <v>79772</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>137068048</v>
       </c>
       <c r="B82" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>137068256</v>
       </c>
       <c r="B83" t="n">
-        <v>80639</v>
+        <v>80642</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>137068031</v>
       </c>
       <c r="B84" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>137068047</v>
       </c>
       <c r="B85" t="n">
-        <v>80640</v>
+        <v>80643</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>137068054</v>
       </c>
       <c r="B86" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>137068060</v>
       </c>
       <c r="B87" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>137068061</v>
       </c>
       <c r="B88" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>137068062</v>
       </c>
       <c r="B89" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>137068077</v>
       </c>
       <c r="B90" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>137068080</v>
       </c>
       <c r="B91" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>137068081</v>
       </c>
       <c r="B92" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>137068090</v>
       </c>
       <c r="B93" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>137068092</v>
       </c>
       <c r="B94" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>137068245</v>
       </c>
       <c r="B95" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>137068248</v>
       </c>
       <c r="B96" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>137068253</v>
       </c>
       <c r="B97" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>137068258</v>
       </c>
       <c r="B98" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>137068274</v>
       </c>
       <c r="B99" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>137068058</v>
       </c>
       <c r="B101" t="n">
-        <v>57211</v>
+        <v>57212</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>137068082</v>
       </c>
       <c r="B104" t="n">
-        <v>99322</v>
+        <v>99327</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>137068030</v>
       </c>
       <c r="B105" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>137068066</v>
       </c>
       <c r="B106" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>137068093</v>
       </c>
       <c r="B107" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>137068243</v>
       </c>
       <c r="B108" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>137068259</v>
       </c>
       <c r="B109" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>137068273</v>
       </c>
       <c r="B110" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>137068043</v>
       </c>
       <c r="B111" t="n">
-        <v>110163</v>
+        <v>110168</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37165-2026 artfynd.xlsx
+++ b/artfynd/A 37165-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068262</v>
       </c>
       <c r="B2" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137068264</v>
       </c>
       <c r="B3" t="n">
-        <v>92112</v>
+        <v>92114</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137068052</v>
       </c>
       <c r="B4" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137068074</v>
       </c>
       <c r="B5" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137068079</v>
       </c>
       <c r="B6" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137068089</v>
       </c>
       <c r="B7" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137068266</v>
       </c>
       <c r="B8" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137068268</v>
       </c>
       <c r="B9" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137068280</v>
       </c>
       <c r="B10" t="n">
-        <v>92433</v>
+        <v>92435</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137068087</v>
       </c>
       <c r="B11" t="n">
-        <v>92158</v>
+        <v>92160</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137068042</v>
       </c>
       <c r="B12" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137068050</v>
       </c>
       <c r="B13" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137068055</v>
       </c>
       <c r="B14" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137068063</v>
       </c>
       <c r="B15" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137068069</v>
       </c>
       <c r="B16" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137068072</v>
       </c>
       <c r="B17" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137068073</v>
       </c>
       <c r="B18" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137068083</v>
       </c>
       <c r="B19" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137068088</v>
       </c>
       <c r="B20" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137068265</v>
       </c>
       <c r="B21" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137068270</v>
       </c>
       <c r="B22" t="n">
-        <v>92162</v>
+        <v>92164</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137068053</v>
       </c>
       <c r="B23" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137068263</v>
       </c>
       <c r="B24" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137068267</v>
       </c>
       <c r="B25" t="n">
-        <v>92594</v>
+        <v>92596</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>137068039</v>
       </c>
       <c r="B30" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>137068082</v>
       </c>
       <c r="B104" t="n">
-        <v>99327</v>
+        <v>99329</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>137068030</v>
       </c>
       <c r="B105" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>137068066</v>
       </c>
       <c r="B106" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>137068093</v>
       </c>
       <c r="B107" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>137068243</v>
       </c>
       <c r="B108" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>137068259</v>
       </c>
       <c r="B109" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>137068273</v>
       </c>
       <c r="B110" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>137068043</v>
       </c>
       <c r="B111" t="n">
-        <v>110168</v>
+        <v>110171</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37165-2026 artfynd.xlsx
+++ b/artfynd/A 37165-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068262</v>
       </c>
       <c r="B2" t="n">
-        <v>92114</v>
+        <v>92119</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137068264</v>
       </c>
       <c r="B3" t="n">
-        <v>92114</v>
+        <v>92119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137068052</v>
       </c>
       <c r="B4" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137068074</v>
       </c>
       <c r="B5" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137068079</v>
       </c>
       <c r="B6" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137068089</v>
       </c>
       <c r="B7" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137068266</v>
       </c>
       <c r="B8" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137068268</v>
       </c>
       <c r="B9" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137068280</v>
       </c>
       <c r="B10" t="n">
-        <v>92435</v>
+        <v>92440</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137068087</v>
       </c>
       <c r="B11" t="n">
-        <v>92160</v>
+        <v>92165</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137068042</v>
       </c>
       <c r="B12" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137068050</v>
       </c>
       <c r="B13" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137068055</v>
       </c>
       <c r="B14" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137068063</v>
       </c>
       <c r="B15" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137068069</v>
       </c>
       <c r="B16" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137068072</v>
       </c>
       <c r="B17" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137068073</v>
       </c>
       <c r="B18" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137068083</v>
       </c>
       <c r="B19" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137068088</v>
       </c>
       <c r="B20" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137068265</v>
       </c>
       <c r="B21" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137068270</v>
       </c>
       <c r="B22" t="n">
-        <v>92164</v>
+        <v>92169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137068053</v>
       </c>
       <c r="B23" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137068263</v>
       </c>
       <c r="B24" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137068267</v>
       </c>
       <c r="B25" t="n">
-        <v>92596</v>
+        <v>92601</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>137068086</v>
       </c>
       <c r="B28" t="n">
-        <v>83384</v>
+        <v>83389</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>137068039</v>
       </c>
       <c r="B30" t="n">
-        <v>92127</v>
+        <v>92132</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>137068025</v>
       </c>
       <c r="B33" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>137068028</v>
       </c>
       <c r="B34" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>137068037</v>
       </c>
       <c r="B35" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>137068044</v>
       </c>
       <c r="B36" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>137068049</v>
       </c>
       <c r="B37" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>137068051</v>
       </c>
       <c r="B38" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>137068057</v>
       </c>
       <c r="B39" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>137068064</v>
       </c>
       <c r="B40" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>137068065</v>
       </c>
       <c r="B41" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137068067</v>
       </c>
       <c r="B42" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>137068071</v>
       </c>
       <c r="B43" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>137068085</v>
       </c>
       <c r="B44" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>137068250</v>
       </c>
       <c r="B45" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>137068257</v>
       </c>
       <c r="B46" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>137068260</v>
       </c>
       <c r="B47" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>137068261</v>
       </c>
       <c r="B48" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>137068271</v>
       </c>
       <c r="B49" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>137068272</v>
       </c>
       <c r="B50" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>137068275</v>
       </c>
       <c r="B51" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>137068277</v>
       </c>
       <c r="B52" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>137068278</v>
       </c>
       <c r="B53" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137068279</v>
       </c>
       <c r="B54" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>137068029</v>
       </c>
       <c r="B55" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>137068033</v>
       </c>
       <c r="B56" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>137068034</v>
       </c>
       <c r="B57" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>137068035</v>
       </c>
       <c r="B58" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>137068252</v>
       </c>
       <c r="B59" t="n">
-        <v>75594</v>
+        <v>75599</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>137068036</v>
       </c>
       <c r="B61" t="n">
-        <v>83490</v>
+        <v>83495</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>137068027</v>
       </c>
       <c r="B62" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>137068038</v>
       </c>
       <c r="B63" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>137068056</v>
       </c>
       <c r="B64" t="n">
-        <v>83507</v>
+        <v>83512</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>137068045</v>
       </c>
       <c r="B74" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>137068068</v>
       </c>
       <c r="B75" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>137068076</v>
       </c>
       <c r="B76" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>137068255</v>
       </c>
       <c r="B77" t="n">
-        <v>80631</v>
+        <v>80636</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>137068032</v>
       </c>
       <c r="B78" t="n">
-        <v>79772</v>
+        <v>79777</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>137068041</v>
       </c>
       <c r="B79" t="n">
-        <v>79772</v>
+        <v>79777</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>137068070</v>
       </c>
       <c r="B80" t="n">
-        <v>79772</v>
+        <v>79777</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>137068084</v>
       </c>
       <c r="B81" t="n">
-        <v>79772</v>
+        <v>79777</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>137068048</v>
       </c>
       <c r="B82" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>137068256</v>
       </c>
       <c r="B83" t="n">
-        <v>80642</v>
+        <v>80647</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>137068031</v>
       </c>
       <c r="B84" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>137068047</v>
       </c>
       <c r="B85" t="n">
-        <v>80643</v>
+        <v>80648</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>137068054</v>
       </c>
       <c r="B86" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>137068060</v>
       </c>
       <c r="B87" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>137068061</v>
       </c>
       <c r="B88" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>137068062</v>
       </c>
       <c r="B89" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>137068077</v>
       </c>
       <c r="B90" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>137068080</v>
       </c>
       <c r="B91" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>137068081</v>
       </c>
       <c r="B92" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>137068090</v>
       </c>
       <c r="B93" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>137068092</v>
       </c>
       <c r="B94" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>137068245</v>
       </c>
       <c r="B95" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>137068248</v>
       </c>
       <c r="B96" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>137068253</v>
       </c>
       <c r="B97" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>137068258</v>
       </c>
       <c r="B98" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>137068274</v>
       </c>
       <c r="B99" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>137068082</v>
       </c>
       <c r="B104" t="n">
-        <v>99329</v>
+        <v>99335</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>137068030</v>
       </c>
       <c r="B105" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>137068066</v>
       </c>
       <c r="B106" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>137068093</v>
       </c>
       <c r="B107" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>137068243</v>
       </c>
       <c r="B108" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>137068259</v>
       </c>
       <c r="B109" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>137068273</v>
       </c>
       <c r="B110" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>137068043</v>
       </c>
       <c r="B111" t="n">
-        <v>110171</v>
+        <v>110177</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37165-2026 artfynd.xlsx
+++ b/artfynd/A 37165-2026 artfynd.xlsx
@@ -12843,7 +12843,7 @@
         <v>137068043</v>
       </c>
       <c r="B111" t="n">
-        <v>110177</v>
+        <v>110178</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37165-2026 artfynd.xlsx
+++ b/artfynd/A 37165-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068262</v>
       </c>
       <c r="B2" t="n">
-        <v>92119</v>
+        <v>92131</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137068264</v>
       </c>
       <c r="B3" t="n">
-        <v>92119</v>
+        <v>92131</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137068052</v>
       </c>
       <c r="B4" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137068074</v>
       </c>
       <c r="B5" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137068079</v>
       </c>
       <c r="B6" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137068089</v>
       </c>
       <c r="B7" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137068266</v>
       </c>
       <c r="B8" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137068268</v>
       </c>
       <c r="B9" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137068280</v>
       </c>
       <c r="B10" t="n">
-        <v>92440</v>
+        <v>92452</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137068087</v>
       </c>
       <c r="B11" t="n">
-        <v>92165</v>
+        <v>92177</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137068042</v>
       </c>
       <c r="B12" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137068050</v>
       </c>
       <c r="B13" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137068055</v>
       </c>
       <c r="B14" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137068063</v>
       </c>
       <c r="B15" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137068069</v>
       </c>
       <c r="B16" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137068072</v>
       </c>
       <c r="B17" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137068073</v>
       </c>
       <c r="B18" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137068083</v>
       </c>
       <c r="B19" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137068088</v>
       </c>
       <c r="B20" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137068265</v>
       </c>
       <c r="B21" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137068270</v>
       </c>
       <c r="B22" t="n">
-        <v>92169</v>
+        <v>92181</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137068053</v>
       </c>
       <c r="B23" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137068263</v>
       </c>
       <c r="B24" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137068267</v>
       </c>
       <c r="B25" t="n">
-        <v>92601</v>
+        <v>92613</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>137068086</v>
       </c>
       <c r="B28" t="n">
-        <v>83389</v>
+        <v>83400</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>137068039</v>
       </c>
       <c r="B30" t="n">
-        <v>92132</v>
+        <v>92144</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>137068025</v>
       </c>
       <c r="B33" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>137068028</v>
       </c>
       <c r="B34" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>137068037</v>
       </c>
       <c r="B35" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>137068044</v>
       </c>
       <c r="B36" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>137068049</v>
       </c>
       <c r="B37" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>137068051</v>
       </c>
       <c r="B38" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>137068057</v>
       </c>
       <c r="B39" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>137068064</v>
       </c>
       <c r="B40" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>137068065</v>
       </c>
       <c r="B41" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137068067</v>
       </c>
       <c r="B42" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>137068071</v>
       </c>
       <c r="B43" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>137068085</v>
       </c>
       <c r="B44" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>137068250</v>
       </c>
       <c r="B45" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>137068257</v>
       </c>
       <c r="B46" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>137068260</v>
       </c>
       <c r="B47" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>137068261</v>
       </c>
       <c r="B48" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>137068271</v>
       </c>
       <c r="B49" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>137068272</v>
       </c>
       <c r="B50" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>137068275</v>
       </c>
       <c r="B51" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>137068277</v>
       </c>
       <c r="B52" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>137068278</v>
       </c>
       <c r="B53" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137068279</v>
       </c>
       <c r="B54" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>137068029</v>
       </c>
       <c r="B55" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>137068033</v>
       </c>
       <c r="B56" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>137068034</v>
       </c>
       <c r="B57" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>137068035</v>
       </c>
       <c r="B58" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>137068252</v>
       </c>
       <c r="B59" t="n">
-        <v>75599</v>
+        <v>75610</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>137068036</v>
       </c>
       <c r="B61" t="n">
-        <v>83495</v>
+        <v>83506</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>137068027</v>
       </c>
       <c r="B62" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>137068038</v>
       </c>
       <c r="B63" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>137068056</v>
       </c>
       <c r="B64" t="n">
-        <v>83512</v>
+        <v>83523</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>137068045</v>
       </c>
       <c r="B74" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>137068068</v>
       </c>
       <c r="B75" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>137068076</v>
       </c>
       <c r="B76" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>137068255</v>
       </c>
       <c r="B77" t="n">
-        <v>80636</v>
+        <v>80647</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>137068032</v>
       </c>
       <c r="B78" t="n">
-        <v>79777</v>
+        <v>79788</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>137068041</v>
       </c>
       <c r="B79" t="n">
-        <v>79777</v>
+        <v>79788</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>137068070</v>
       </c>
       <c r="B80" t="n">
-        <v>79777</v>
+        <v>79788</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>137068084</v>
       </c>
       <c r="B81" t="n">
-        <v>79777</v>
+        <v>79788</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>137068048</v>
       </c>
       <c r="B82" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>137068256</v>
       </c>
       <c r="B83" t="n">
-        <v>80647</v>
+        <v>80658</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>137068031</v>
       </c>
       <c r="B84" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>137068047</v>
       </c>
       <c r="B85" t="n">
-        <v>80648</v>
+        <v>80659</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>137068082</v>
       </c>
       <c r="B104" t="n">
-        <v>99335</v>
+        <v>99347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>137068030</v>
       </c>
       <c r="B105" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>137068066</v>
       </c>
       <c r="B106" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>137068093</v>
       </c>
       <c r="B107" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>137068243</v>
       </c>
       <c r="B108" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>137068259</v>
       </c>
       <c r="B109" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>137068273</v>
       </c>
       <c r="B110" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>137068043</v>
       </c>
       <c r="B111" t="n">
-        <v>110178</v>
+        <v>110190</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37165-2026 artfynd.xlsx
+++ b/artfynd/A 37165-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068262</v>
       </c>
       <c r="B2" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137068264</v>
       </c>
       <c r="B3" t="n">
-        <v>92131</v>
+        <v>92132</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137068052</v>
       </c>
       <c r="B4" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137068074</v>
       </c>
       <c r="B5" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137068079</v>
       </c>
       <c r="B6" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137068089</v>
       </c>
       <c r="B7" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137068266</v>
       </c>
       <c r="B8" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137068268</v>
       </c>
       <c r="B9" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137068280</v>
       </c>
       <c r="B10" t="n">
-        <v>92452</v>
+        <v>92453</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137068087</v>
       </c>
       <c r="B11" t="n">
-        <v>92177</v>
+        <v>92178</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137068042</v>
       </c>
       <c r="B12" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137068050</v>
       </c>
       <c r="B13" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137068055</v>
       </c>
       <c r="B14" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137068063</v>
       </c>
       <c r="B15" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137068069</v>
       </c>
       <c r="B16" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137068072</v>
       </c>
       <c r="B17" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137068073</v>
       </c>
       <c r="B18" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137068083</v>
       </c>
       <c r="B19" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137068088</v>
       </c>
       <c r="B20" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137068265</v>
       </c>
       <c r="B21" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137068270</v>
       </c>
       <c r="B22" t="n">
-        <v>92181</v>
+        <v>92182</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137068053</v>
       </c>
       <c r="B23" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137068263</v>
       </c>
       <c r="B24" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137068267</v>
       </c>
       <c r="B25" t="n">
-        <v>92613</v>
+        <v>92614</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>137068086</v>
       </c>
       <c r="B28" t="n">
-        <v>83400</v>
+        <v>83401</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>137068039</v>
       </c>
       <c r="B30" t="n">
-        <v>92144</v>
+        <v>92145</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>137068025</v>
       </c>
       <c r="B33" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>137068028</v>
       </c>
       <c r="B34" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>137068037</v>
       </c>
       <c r="B35" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>137068044</v>
       </c>
       <c r="B36" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>137068049</v>
       </c>
       <c r="B37" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>137068051</v>
       </c>
       <c r="B38" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>137068057</v>
       </c>
       <c r="B39" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>137068064</v>
       </c>
       <c r="B40" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>137068065</v>
       </c>
       <c r="B41" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137068067</v>
       </c>
       <c r="B42" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>137068071</v>
       </c>
       <c r="B43" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>137068085</v>
       </c>
       <c r="B44" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>137068250</v>
       </c>
       <c r="B45" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>137068257</v>
       </c>
       <c r="B46" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>137068260</v>
       </c>
       <c r="B47" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>137068261</v>
       </c>
       <c r="B48" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>137068271</v>
       </c>
       <c r="B49" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>137068272</v>
       </c>
       <c r="B50" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>137068275</v>
       </c>
       <c r="B51" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>137068277</v>
       </c>
       <c r="B52" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>137068278</v>
       </c>
       <c r="B53" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137068279</v>
       </c>
       <c r="B54" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>137068036</v>
       </c>
       <c r="B61" t="n">
-        <v>83506</v>
+        <v>83507</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>137068027</v>
       </c>
       <c r="B62" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>137068038</v>
       </c>
       <c r="B63" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>137068056</v>
       </c>
       <c r="B64" t="n">
-        <v>83523</v>
+        <v>83524</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>137068045</v>
       </c>
       <c r="B74" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>137068068</v>
       </c>
       <c r="B75" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>137068076</v>
       </c>
       <c r="B76" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>137068255</v>
       </c>
       <c r="B77" t="n">
-        <v>80647</v>
+        <v>80648</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>137068032</v>
       </c>
       <c r="B78" t="n">
-        <v>79788</v>
+        <v>79789</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>137068041</v>
       </c>
       <c r="B79" t="n">
-        <v>79788</v>
+        <v>79789</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>137068070</v>
       </c>
       <c r="B80" t="n">
-        <v>79788</v>
+        <v>79789</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>137068084</v>
       </c>
       <c r="B81" t="n">
-        <v>79788</v>
+        <v>79789</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>137068048</v>
       </c>
       <c r="B82" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>137068256</v>
       </c>
       <c r="B83" t="n">
-        <v>80658</v>
+        <v>80659</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>137068031</v>
       </c>
       <c r="B84" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>137068047</v>
       </c>
       <c r="B85" t="n">
-        <v>80659</v>
+        <v>80660</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>137068082</v>
       </c>
       <c r="B104" t="n">
-        <v>99347</v>
+        <v>99348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>137068030</v>
       </c>
       <c r="B105" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>137068066</v>
       </c>
       <c r="B106" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>137068093</v>
       </c>
       <c r="B107" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>137068243</v>
       </c>
       <c r="B108" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>137068259</v>
       </c>
       <c r="B109" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>137068273</v>
       </c>
       <c r="B110" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>137068043</v>
       </c>
       <c r="B111" t="n">
-        <v>110190</v>
+        <v>110191</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37165-2026 artfynd.xlsx
+++ b/artfynd/A 37165-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068262</v>
       </c>
       <c r="B2" t="n">
-        <v>92132</v>
+        <v>92135</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137068264</v>
       </c>
       <c r="B3" t="n">
-        <v>92132</v>
+        <v>92135</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137068052</v>
       </c>
       <c r="B4" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137068074</v>
       </c>
       <c r="B5" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137068079</v>
       </c>
       <c r="B6" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137068089</v>
       </c>
       <c r="B7" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137068266</v>
       </c>
       <c r="B8" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137068268</v>
       </c>
       <c r="B9" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137068280</v>
       </c>
       <c r="B10" t="n">
-        <v>92453</v>
+        <v>92456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137068087</v>
       </c>
       <c r="B11" t="n">
-        <v>92178</v>
+        <v>92181</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137068042</v>
       </c>
       <c r="B12" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137068050</v>
       </c>
       <c r="B13" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137068055</v>
       </c>
       <c r="B14" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137068063</v>
       </c>
       <c r="B15" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137068069</v>
       </c>
       <c r="B16" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137068072</v>
       </c>
       <c r="B17" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137068073</v>
       </c>
       <c r="B18" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137068083</v>
       </c>
       <c r="B19" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137068088</v>
       </c>
       <c r="B20" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137068265</v>
       </c>
       <c r="B21" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137068270</v>
       </c>
       <c r="B22" t="n">
-        <v>92182</v>
+        <v>92185</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137068053</v>
       </c>
       <c r="B23" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137068263</v>
       </c>
       <c r="B24" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137068267</v>
       </c>
       <c r="B25" t="n">
-        <v>92614</v>
+        <v>92617</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>137068086</v>
       </c>
       <c r="B28" t="n">
-        <v>83401</v>
+        <v>83403</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>137068039</v>
       </c>
       <c r="B30" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>137068025</v>
       </c>
       <c r="B33" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>137068028</v>
       </c>
       <c r="B34" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>137068037</v>
       </c>
       <c r="B35" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>137068044</v>
       </c>
       <c r="B36" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>137068049</v>
       </c>
       <c r="B37" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>137068051</v>
       </c>
       <c r="B38" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>137068057</v>
       </c>
       <c r="B39" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>137068064</v>
       </c>
       <c r="B40" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>137068065</v>
       </c>
       <c r="B41" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137068067</v>
       </c>
       <c r="B42" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>137068071</v>
       </c>
       <c r="B43" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>137068085</v>
       </c>
       <c r="B44" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>137068250</v>
       </c>
       <c r="B45" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>137068257</v>
       </c>
       <c r="B46" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>137068260</v>
       </c>
       <c r="B47" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>137068261</v>
       </c>
       <c r="B48" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>137068271</v>
       </c>
       <c r="B49" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>137068272</v>
       </c>
       <c r="B50" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>137068275</v>
       </c>
       <c r="B51" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>137068277</v>
       </c>
       <c r="B52" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>137068278</v>
       </c>
       <c r="B53" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137068279</v>
       </c>
       <c r="B54" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>137068036</v>
       </c>
       <c r="B61" t="n">
-        <v>83507</v>
+        <v>83509</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>137068027</v>
       </c>
       <c r="B62" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>137068038</v>
       </c>
       <c r="B63" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>137068056</v>
       </c>
       <c r="B64" t="n">
-        <v>83524</v>
+        <v>83526</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>137068045</v>
       </c>
       <c r="B74" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>137068068</v>
       </c>
       <c r="B75" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>137068076</v>
       </c>
       <c r="B76" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>137068255</v>
       </c>
       <c r="B77" t="n">
-        <v>80648</v>
+        <v>80650</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>137068032</v>
       </c>
       <c r="B78" t="n">
-        <v>79789</v>
+        <v>79791</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>137068041</v>
       </c>
       <c r="B79" t="n">
-        <v>79789</v>
+        <v>79791</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>137068070</v>
       </c>
       <c r="B80" t="n">
-        <v>79789</v>
+        <v>79791</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>137068084</v>
       </c>
       <c r="B81" t="n">
-        <v>79789</v>
+        <v>79791</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>137068048</v>
       </c>
       <c r="B82" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>137068256</v>
       </c>
       <c r="B83" t="n">
-        <v>80659</v>
+        <v>80661</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>137068031</v>
       </c>
       <c r="B84" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>137068047</v>
       </c>
       <c r="B85" t="n">
-        <v>80660</v>
+        <v>80662</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>137068082</v>
       </c>
       <c r="B104" t="n">
-        <v>99348</v>
+        <v>99351</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>137068030</v>
       </c>
       <c r="B105" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>137068066</v>
       </c>
       <c r="B106" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>137068093</v>
       </c>
       <c r="B107" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>137068243</v>
       </c>
       <c r="B108" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>137068259</v>
       </c>
       <c r="B109" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>137068273</v>
       </c>
       <c r="B110" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>137068043</v>
       </c>
       <c r="B111" t="n">
-        <v>110191</v>
+        <v>110194</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>

--- a/artfynd/A 37165-2026 artfynd.xlsx
+++ b/artfynd/A 37165-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137068262</v>
       </c>
       <c r="B2" t="n">
-        <v>92135</v>
+        <v>92139</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -795,7 +795,7 @@
         <v>137068264</v>
       </c>
       <c r="B3" t="n">
-        <v>92135</v>
+        <v>92139</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -907,7 +907,7 @@
         <v>137068052</v>
       </c>
       <c r="B4" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>137068074</v>
       </c>
       <c r="B5" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1131,7 +1131,7 @@
         <v>137068079</v>
       </c>
       <c r="B6" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1243,7 +1243,7 @@
         <v>137068089</v>
       </c>
       <c r="B7" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>137068266</v>
       </c>
       <c r="B8" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1467,7 +1467,7 @@
         <v>137068268</v>
       </c>
       <c r="B9" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1579,7 +1579,7 @@
         <v>137068280</v>
       </c>
       <c r="B10" t="n">
-        <v>92456</v>
+        <v>92460</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1691,7 +1691,7 @@
         <v>137068087</v>
       </c>
       <c r="B11" t="n">
-        <v>92181</v>
+        <v>92185</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1803,7 +1803,7 @@
         <v>137068042</v>
       </c>
       <c r="B12" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1915,7 +1915,7 @@
         <v>137068050</v>
       </c>
       <c r="B13" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2027,7 +2027,7 @@
         <v>137068055</v>
       </c>
       <c r="B14" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2139,7 +2139,7 @@
         <v>137068063</v>
       </c>
       <c r="B15" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2251,7 +2251,7 @@
         <v>137068069</v>
       </c>
       <c r="B16" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2363,7 +2363,7 @@
         <v>137068072</v>
       </c>
       <c r="B17" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2475,7 +2475,7 @@
         <v>137068073</v>
       </c>
       <c r="B18" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2587,7 +2587,7 @@
         <v>137068083</v>
       </c>
       <c r="B19" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2699,7 +2699,7 @@
         <v>137068088</v>
       </c>
       <c r="B20" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2811,7 +2811,7 @@
         <v>137068265</v>
       </c>
       <c r="B21" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2923,7 +2923,7 @@
         <v>137068270</v>
       </c>
       <c r="B22" t="n">
-        <v>92185</v>
+        <v>92189</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3035,7 +3035,7 @@
         <v>137068053</v>
       </c>
       <c r="B23" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3147,7 +3147,7 @@
         <v>137068263</v>
       </c>
       <c r="B24" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3259,7 +3259,7 @@
         <v>137068267</v>
       </c>
       <c r="B25" t="n">
-        <v>92617</v>
+        <v>92621</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3576,7 +3576,7 @@
         <v>137068086</v>
       </c>
       <c r="B28" t="n">
-        <v>83403</v>
+        <v>83407</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3790,7 +3790,7 @@
         <v>137068039</v>
       </c>
       <c r="B30" t="n">
-        <v>92148</v>
+        <v>92152</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4106,7 +4106,7 @@
         <v>137068025</v>
       </c>
       <c r="B33" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4218,7 +4218,7 @@
         <v>137068028</v>
       </c>
       <c r="B34" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
         <v>137068037</v>
       </c>
       <c r="B35" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4442,7 +4442,7 @@
         <v>137068044</v>
       </c>
       <c r="B36" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4554,7 +4554,7 @@
         <v>137068049</v>
       </c>
       <c r="B37" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4666,7 +4666,7 @@
         <v>137068051</v>
       </c>
       <c r="B38" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4778,7 +4778,7 @@
         <v>137068057</v>
       </c>
       <c r="B39" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4890,7 +4890,7 @@
         <v>137068064</v>
       </c>
       <c r="B40" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5002,7 +5002,7 @@
         <v>137068065</v>
       </c>
       <c r="B41" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5114,7 +5114,7 @@
         <v>137068067</v>
       </c>
       <c r="B42" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>137068071</v>
       </c>
       <c r="B43" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5338,7 +5338,7 @@
         <v>137068085</v>
       </c>
       <c r="B44" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5450,7 +5450,7 @@
         <v>137068250</v>
       </c>
       <c r="B45" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5562,7 +5562,7 @@
         <v>137068257</v>
       </c>
       <c r="B46" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5674,7 +5674,7 @@
         <v>137068260</v>
       </c>
       <c r="B47" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5786,7 +5786,7 @@
         <v>137068261</v>
       </c>
       <c r="B48" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5898,7 +5898,7 @@
         <v>137068271</v>
       </c>
       <c r="B49" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6010,7 +6010,7 @@
         <v>137068272</v>
       </c>
       <c r="B50" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6122,7 +6122,7 @@
         <v>137068275</v>
       </c>
       <c r="B51" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6234,7 +6234,7 @@
         <v>137068277</v>
       </c>
       <c r="B52" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6346,7 +6346,7 @@
         <v>137068278</v>
       </c>
       <c r="B53" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6458,7 +6458,7 @@
         <v>137068279</v>
       </c>
       <c r="B54" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6570,7 +6570,7 @@
         <v>137068029</v>
       </c>
       <c r="B55" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6682,7 +6682,7 @@
         <v>137068033</v>
       </c>
       <c r="B56" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6794,7 +6794,7 @@
         <v>137068034</v>
       </c>
       <c r="B57" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6906,7 +6906,7 @@
         <v>137068035</v>
       </c>
       <c r="B58" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7018,7 +7018,7 @@
         <v>137068252</v>
       </c>
       <c r="B59" t="n">
-        <v>75610</v>
+        <v>75614</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7232,7 +7232,7 @@
         <v>137068036</v>
       </c>
       <c r="B61" t="n">
-        <v>83509</v>
+        <v>83513</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>137068027</v>
       </c>
       <c r="B62" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7456,7 +7456,7 @@
         <v>137068038</v>
       </c>
       <c r="B63" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7568,7 +7568,7 @@
         <v>137068056</v>
       </c>
       <c r="B64" t="n">
-        <v>83526</v>
+        <v>83530</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -8598,7 +8598,7 @@
         <v>137068045</v>
       </c>
       <c r="B74" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8710,7 +8710,7 @@
         <v>137068068</v>
       </c>
       <c r="B75" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8822,7 +8822,7 @@
         <v>137068076</v>
       </c>
       <c r="B76" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8934,7 +8934,7 @@
         <v>137068255</v>
       </c>
       <c r="B77" t="n">
-        <v>80650</v>
+        <v>80654</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9046,7 +9046,7 @@
         <v>137068032</v>
       </c>
       <c r="B78" t="n">
-        <v>79791</v>
+        <v>79795</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9158,7 +9158,7 @@
         <v>137068041</v>
       </c>
       <c r="B79" t="n">
-        <v>79791</v>
+        <v>79795</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9270,7 +9270,7 @@
         <v>137068070</v>
       </c>
       <c r="B80" t="n">
-        <v>79791</v>
+        <v>79795</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9382,7 +9382,7 @@
         <v>137068084</v>
       </c>
       <c r="B81" t="n">
-        <v>79791</v>
+        <v>79795</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9494,7 +9494,7 @@
         <v>137068048</v>
       </c>
       <c r="B82" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9606,7 +9606,7 @@
         <v>137068256</v>
       </c>
       <c r="B83" t="n">
-        <v>80661</v>
+        <v>80665</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9718,7 +9718,7 @@
         <v>137068031</v>
       </c>
       <c r="B84" t="n">
-        <v>80662</v>
+        <v>80666</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9830,7 +9830,7 @@
         <v>137068047</v>
       </c>
       <c r="B85" t="n">
-        <v>80662</v>
+        <v>80666</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9942,7 +9942,7 @@
         <v>137068054</v>
       </c>
       <c r="B86" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10060,7 +10060,7 @@
         <v>137068060</v>
       </c>
       <c r="B87" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10178,7 +10178,7 @@
         <v>137068061</v>
       </c>
       <c r="B88" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10296,7 +10296,7 @@
         <v>137068062</v>
       </c>
       <c r="B89" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10414,7 +10414,7 @@
         <v>137068077</v>
       </c>
       <c r="B90" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10532,7 +10532,7 @@
         <v>137068080</v>
       </c>
       <c r="B91" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10650,7 +10650,7 @@
         <v>137068081</v>
       </c>
       <c r="B92" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10768,7 +10768,7 @@
         <v>137068090</v>
       </c>
       <c r="B93" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10886,7 +10886,7 @@
         <v>137068092</v>
       </c>
       <c r="B94" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -11004,7 +11004,7 @@
         <v>137068245</v>
       </c>
       <c r="B95" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -11122,7 +11122,7 @@
         <v>137068248</v>
       </c>
       <c r="B96" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11240,7 +11240,7 @@
         <v>137068253</v>
       </c>
       <c r="B97" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11358,7 +11358,7 @@
         <v>137068258</v>
       </c>
       <c r="B98" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11476,7 +11476,7 @@
         <v>137068274</v>
       </c>
       <c r="B99" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11696,7 +11696,7 @@
         <v>137068058</v>
       </c>
       <c r="B101" t="n">
-        <v>57212</v>
+        <v>57215</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -12017,7 +12017,7 @@
         <v>137068082</v>
       </c>
       <c r="B104" t="n">
-        <v>99351</v>
+        <v>99355</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12129,7 +12129,7 @@
         <v>137068030</v>
       </c>
       <c r="B105" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12250,7 +12250,7 @@
         <v>137068066</v>
       </c>
       <c r="B106" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12371,7 +12371,7 @@
         <v>137068093</v>
       </c>
       <c r="B107" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12492,7 +12492,7 @@
         <v>137068243</v>
       </c>
       <c r="B108" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12609,7 +12609,7 @@
         <v>137068259</v>
       </c>
       <c r="B109" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12726,7 +12726,7 @@
         <v>137068273</v>
       </c>
       <c r="B110" t="n">
-        <v>99434</v>
+        <v>99438</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12843,7 +12843,7 @@
         <v>137068043</v>
       </c>
       <c r="B111" t="n">
-        <v>110194</v>
+        <v>110200</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
